--- a/artfynd/A 13873-2022 artfynd.xlsx
+++ b/artfynd/A 13873-2022 artfynd.xlsx
@@ -3841,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119539920</v>
+        <v>119539917</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>79473</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3853,25 +3853,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540403</v>
+        <v>540406</v>
       </c>
       <c r="R30" t="n">
-        <v>6943409</v>
+        <v>6943382</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3934,7 +3934,12 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk morän</t>
+          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>150-årig asp</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3956,10 +3961,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119539917</v>
+        <v>119539878</v>
       </c>
       <c r="B31" t="n">
-        <v>79473</v>
+        <v>78171</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3972,26 +3977,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4000,10 +4005,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540406</v>
+        <v>540416</v>
       </c>
       <c r="R31" t="n">
-        <v>6943382</v>
+        <v>6943681</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4049,12 +4054,12 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>150-årig asp</t>
+          <t>tallågor efter fallna torrakor</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4076,10 +4081,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119539878</v>
+        <v>119539889</v>
       </c>
       <c r="B32" t="n">
-        <v>78171</v>
+        <v>91310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4088,30 +4093,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>1958</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4120,10 +4125,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540416</v>
+        <v>540373</v>
       </c>
       <c r="R32" t="n">
-        <v>6943681</v>
+        <v>6943495</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4169,12 +4174,12 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>tallågor efter fallna torrakor</t>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4196,10 +4201,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119539884</v>
+        <v>119539902</v>
       </c>
       <c r="B33" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4212,21 +4217,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4240,10 +4245,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540340</v>
+        <v>540358</v>
       </c>
       <c r="R33" t="n">
-        <v>6943926</v>
+        <v>6943621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4289,12 +4294,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>sandfläck med lav</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119539902</v>
+        <v>119539920</v>
       </c>
       <c r="B34" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4328,25 +4328,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540358</v>
+        <v>540403</v>
       </c>
       <c r="R34" t="n">
-        <v>6943621</v>
+        <v>6943409</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig lövrik tallnaturskog på frisk morän</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4431,10 +4431,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119539889</v>
+        <v>119539884</v>
       </c>
       <c r="B35" t="n">
-        <v>91310</v>
+        <v>91832</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4443,25 +4443,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1958</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540373</v>
+        <v>540340</v>
       </c>
       <c r="R35" t="n">
-        <v>6943495</v>
+        <v>6943926</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5031,10 +5031,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119539880</v>
+        <v>119539929</v>
       </c>
       <c r="B40" t="n">
-        <v>78263</v>
+        <v>91856</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5047,34 +5047,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540454</v>
+        <v>540360</v>
       </c>
       <c r="R40" t="n">
-        <v>6943707</v>
+        <v>6943180</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5120,12 +5124,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>brandhögstubbar</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5147,7 +5146,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119539896</v>
+        <v>119539880</v>
       </c>
       <c r="B41" t="n">
         <v>78263</v>
@@ -5180,21 +5179,17 @@
           <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540348</v>
+        <v>540454</v>
       </c>
       <c r="R41" t="n">
-        <v>6943733</v>
+        <v>6943707</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5240,12 +5235,12 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>8 m hög, 50 cm bred skorstenshögstubbe med brandspår</t>
+          <t>brandhögstubbar</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5267,7 +5262,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119539925</v>
+        <v>119539896</v>
       </c>
       <c r="B42" t="n">
         <v>78263</v>
@@ -5302,7 +5297,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5311,10 +5306,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540347</v>
+        <v>540348</v>
       </c>
       <c r="R42" t="n">
-        <v>6943300</v>
+        <v>6943733</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5360,12 +5355,12 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>brandhögstubbar</t>
+          <t>8 m hög, 50 cm bred skorstenshögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5387,10 +5382,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119539929</v>
+        <v>119539925</v>
       </c>
       <c r="B43" t="n">
-        <v>91856</v>
+        <v>78263</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5403,26 +5398,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5431,10 +5426,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540360</v>
+        <v>540347</v>
       </c>
       <c r="R43" t="n">
-        <v>6943180</v>
+        <v>6943300</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5481,6 +5476,11 @@
       <c r="AI43" t="inlineStr">
         <is>
           <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>brandhögstubbar</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119539932</v>
+        <v>119539899</v>
       </c>
       <c r="B48" t="n">
-        <v>80483</v>
+        <v>90807</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5984,25 +5984,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1049</v>
+        <v>65</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540431</v>
+        <v>540341</v>
       </c>
       <c r="R48" t="n">
-        <v>6943279</v>
+        <v>6943727</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>gammal torraka med avfallande splint, 30 cm bred</t>
+          <t>gammal tallåga som murknar i ena änden</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6092,10 +6092,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119539899</v>
+        <v>119539936</v>
       </c>
       <c r="B49" t="n">
-        <v>90807</v>
+        <v>78171</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6104,25 +6104,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540341</v>
+        <v>540517</v>
       </c>
       <c r="R49" t="n">
-        <v>6943727</v>
+        <v>6943388</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>gammal tallåga som murknar i ena änden</t>
+          <t>grov gammal tallåga, hängande på block</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119539936</v>
+        <v>119539877</v>
       </c>
       <c r="B50" t="n">
         <v>78171</v>
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540517</v>
+        <v>540487</v>
       </c>
       <c r="R50" t="n">
-        <v>6943388</v>
+        <v>6943562</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>grov gammal tallåga, hängande på block</t>
+          <t>gammal grov tallåga</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6332,10 +6332,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119539877</v>
+        <v>119539932</v>
       </c>
       <c r="B51" t="n">
-        <v>78171</v>
+        <v>80483</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540487</v>
+        <v>540431</v>
       </c>
       <c r="R51" t="n">
-        <v>6943562</v>
+        <v>6943279</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>gammal grov tallåga</t>
+          <t>gammal torraka med avfallande splint, 30 cm bred</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6452,10 +6452,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119539938</v>
+        <v>119539901</v>
       </c>
       <c r="B52" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6468,21 +6468,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540548</v>
+        <v>540369</v>
       </c>
       <c r="R52" t="n">
-        <v>6943249</v>
+        <v>6943646</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6545,12 +6545,12 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>gammal ihålig rest av grov gammal tallåga</t>
+          <t>50 cm grov och hög skorstenshögstubbe med bohål</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6572,10 +6572,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119539901</v>
+        <v>119539938</v>
       </c>
       <c r="B53" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6588,21 +6588,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540369</v>
+        <v>540548</v>
       </c>
       <c r="R53" t="n">
-        <v>6943646</v>
+        <v>6943249</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>50 cm grov och hög skorstenshögstubbe med bohål</t>
+          <t>gammal ihålig rest av grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119539893</v>
+        <v>119539903</v>
       </c>
       <c r="B59" t="n">
-        <v>90807</v>
+        <v>91856</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7299,30 +7299,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>65</v>
+        <v>2059</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540290</v>
+        <v>540360</v>
       </c>
       <c r="R59" t="n">
-        <v>6943642</v>
+        <v>6943524</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7380,12 +7380,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7407,10 +7402,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119539918</v>
+        <v>119539913</v>
       </c>
       <c r="B60" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7423,21 +7418,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7451,10 +7446,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540396</v>
+        <v>540440</v>
       </c>
       <c r="R60" t="n">
-        <v>6943402</v>
+        <v>6943388</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7500,12 +7495,12 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>grov gammal tallåga, upphängd på block</t>
+          <t>grov gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7527,7 +7522,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119539898</v>
+        <v>119539918</v>
       </c>
       <c r="B61" t="n">
         <v>78171</v>
@@ -7571,10 +7566,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540341</v>
+        <v>540396</v>
       </c>
       <c r="R61" t="n">
-        <v>6943727</v>
+        <v>6943402</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7620,12 +7615,12 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>gammal tallåga som murknar i ena änden</t>
+          <t>grov gammal tallåga, upphängd på block</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7647,10 +7642,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119539903</v>
+        <v>119539898</v>
       </c>
       <c r="B62" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7663,21 +7658,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7691,10 +7686,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540360</v>
+        <v>540341</v>
       </c>
       <c r="R62" t="n">
-        <v>6943524</v>
+        <v>6943727</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7740,7 +7735,12 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>gammal tallåga som murknar i ena änden</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7762,10 +7762,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119539913</v>
+        <v>119539893</v>
       </c>
       <c r="B63" t="n">
-        <v>78263</v>
+        <v>90807</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7774,30 +7774,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7806,10 +7806,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540440</v>
+        <v>540290</v>
       </c>
       <c r="R63" t="n">
-        <v>6943388</v>
+        <v>6943642</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>grov gammal brandhögstubbe</t>
+          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8472,7 +8472,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119539891</v>
+        <v>119539904</v>
       </c>
       <c r="B69" t="n">
         <v>92030</v>
@@ -8516,10 +8516,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540309</v>
+        <v>540327</v>
       </c>
       <c r="R69" t="n">
-        <v>6943634</v>
+        <v>6943521</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8565,12 +8565,12 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>grov tallåga av fallen torraka, upphängd på block</t>
+          <t>gammal tallågerest med brandspår</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8592,10 +8592,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119539934</v>
+        <v>119539891</v>
       </c>
       <c r="B70" t="n">
-        <v>78262</v>
+        <v>92030</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8608,21 +8608,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8636,10 +8636,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540502</v>
+        <v>540309</v>
       </c>
       <c r="R70" t="n">
-        <v>6943408</v>
+        <v>6943634</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>grov gammal tallhögstubbe med kolade ytor</t>
+          <t>grov tallåga av fallen torraka, upphängd på block</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8832,10 +8832,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119539904</v>
+        <v>119539934</v>
       </c>
       <c r="B72" t="n">
-        <v>92030</v>
+        <v>78262</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8848,21 +8848,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8876,10 +8876,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540327</v>
+        <v>540502</v>
       </c>
       <c r="R72" t="n">
-        <v>6943521</v>
+        <v>6943408</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>gammal tallågerest med brandspår</t>
+          <t>grov gammal tallhögstubbe med kolade ytor</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8952,10 +8952,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119539879</v>
+        <v>119539906</v>
       </c>
       <c r="B73" t="n">
-        <v>92030</v>
+        <v>78171</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8968,21 +8968,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8996,10 +8996,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540440</v>
+        <v>540330</v>
       </c>
       <c r="R73" t="n">
-        <v>6943698</v>
+        <v>6943510</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9045,12 +9045,12 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>inuti grov, gammal och murken tallåga</t>
+          <t>gammal tallågerest</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9072,10 +9072,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119539906</v>
+        <v>119539879</v>
       </c>
       <c r="B74" t="n">
-        <v>78171</v>
+        <v>92030</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9088,21 +9088,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540330</v>
+        <v>540440</v>
       </c>
       <c r="R74" t="n">
-        <v>6943510</v>
+        <v>6943698</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>gammal tallågerest</t>
+          <t>inuti grov, gammal och murken tallåga</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9312,10 +9312,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119539886</v>
+        <v>119539905</v>
       </c>
       <c r="B76" t="n">
-        <v>79115</v>
+        <v>90712</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9324,25 +9324,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540305</v>
+        <v>540322</v>
       </c>
       <c r="R76" t="n">
-        <v>6943840</v>
+        <v>6943516</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>torr och hård gammal tallhögstubbe</t>
+          <t>50 cm grov gammal tallåga efter fallen bränd torraka, upphängd</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9432,10 +9432,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119539905</v>
+        <v>119539886</v>
       </c>
       <c r="B77" t="n">
-        <v>90712</v>
+        <v>79115</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9444,25 +9444,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540322</v>
+        <v>540305</v>
       </c>
       <c r="R77" t="n">
-        <v>6943516</v>
+        <v>6943840</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>50 cm grov gammal tallåga efter fallen bränd torraka, upphängd</t>
+          <t>torr och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10022,10 +10022,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119539910</v>
+        <v>119539881</v>
       </c>
       <c r="B82" t="n">
-        <v>89253</v>
+        <v>90807</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10038,21 +10038,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1599</v>
+        <v>65</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10066,10 +10066,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540408</v>
+        <v>540423</v>
       </c>
       <c r="R82" t="n">
-        <v>6943426</v>
+        <v>6943766</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10110,18 +10110,17 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>lågörtsmark</t>
+          <t>bränd tallågerest</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10143,10 +10142,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119539921</v>
+        <v>119539910</v>
       </c>
       <c r="B83" t="n">
-        <v>91834</v>
+        <v>89253</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10155,25 +10154,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>1599</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -10187,10 +10186,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540400</v>
+        <v>540408</v>
       </c>
       <c r="R83" t="n">
-        <v>6943414</v>
+        <v>6943426</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10231,12 +10230,18 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog</t>
+          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>lågörtsmark</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10258,10 +10263,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119539881</v>
+        <v>119539930</v>
       </c>
       <c r="B84" t="n">
-        <v>90807</v>
+        <v>92030</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10270,25 +10275,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10302,10 +10307,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540423</v>
+        <v>540379</v>
       </c>
       <c r="R84" t="n">
-        <v>6943766</v>
+        <v>6943193</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10351,12 +10356,12 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>bränd tallågerest</t>
+          <t>äldre tallstock</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10378,10 +10383,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119539930</v>
+        <v>119539921</v>
       </c>
       <c r="B85" t="n">
-        <v>92030</v>
+        <v>91834</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10394,21 +10399,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10422,10 +10427,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540379</v>
+        <v>540400</v>
       </c>
       <c r="R85" t="n">
-        <v>6943193</v>
+        <v>6943414</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10471,12 +10476,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>äldre tallstock</t>
+          <t>140-årig lövrik tallnaturskog</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>

--- a/artfynd/A 13873-2022 artfynd.xlsx
+++ b/artfynd/A 13873-2022 artfynd.xlsx
@@ -6452,10 +6452,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119539901</v>
+        <v>119539938</v>
       </c>
       <c r="B52" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6468,21 +6468,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540369</v>
+        <v>540548</v>
       </c>
       <c r="R52" t="n">
-        <v>6943646</v>
+        <v>6943249</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6545,12 +6545,12 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>50 cm grov och hög skorstenshögstubbe med bohål</t>
+          <t>gammal ihålig rest av grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6572,10 +6572,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119539938</v>
+        <v>119539901</v>
       </c>
       <c r="B53" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6588,21 +6588,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540548</v>
+        <v>540369</v>
       </c>
       <c r="R53" t="n">
-        <v>6943249</v>
+        <v>6943646</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>gammal ihålig rest av grov gammal tallåga</t>
+          <t>50 cm grov och hög skorstenshögstubbe med bohål</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6692,10 +6692,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119539909</v>
+        <v>119539890</v>
       </c>
       <c r="B54" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6708,21 +6708,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540370</v>
+        <v>540393</v>
       </c>
       <c r="R54" t="n">
-        <v>6943446</v>
+        <v>6943526</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6785,12 +6785,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>grov gammal tallågerest</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6812,10 +6807,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119539895</v>
+        <v>119539909</v>
       </c>
       <c r="B55" t="n">
-        <v>90712</v>
+        <v>78171</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6824,25 +6819,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6856,10 +6851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540287</v>
+        <v>540370</v>
       </c>
       <c r="R55" t="n">
-        <v>6943686</v>
+        <v>6943446</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6905,12 +6900,12 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>gammal murken rest av tallåga</t>
+          <t>grov gammal tallågerest</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6932,7 +6927,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119539882</v>
+        <v>119539895</v>
       </c>
       <c r="B56" t="n">
         <v>90712</v>
@@ -6976,10 +6971,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540460</v>
+        <v>540287</v>
       </c>
       <c r="R56" t="n">
-        <v>6943791</v>
+        <v>6943686</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7025,12 +7020,12 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>mycket grov gammal tallåga, upphängd på block</t>
+          <t>gammal murken rest av tallåga</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7052,10 +7047,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119539890</v>
+        <v>119539882</v>
       </c>
       <c r="B57" t="n">
-        <v>91834</v>
+        <v>90712</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7064,25 +7059,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>1503</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7096,10 +7091,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540393</v>
+        <v>540460</v>
       </c>
       <c r="R57" t="n">
-        <v>6943526</v>
+        <v>6943791</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7145,7 +7140,12 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog på frisk rismark</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>mycket grov gammal tallåga, upphängd på block</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119539903</v>
+        <v>119539893</v>
       </c>
       <c r="B59" t="n">
-        <v>91856</v>
+        <v>90807</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7299,30 +7299,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2059</v>
+        <v>65</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540360</v>
+        <v>540290</v>
       </c>
       <c r="R59" t="n">
-        <v>6943524</v>
+        <v>6943642</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7380,7 +7380,12 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7402,10 +7407,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119539913</v>
+        <v>119539918</v>
       </c>
       <c r="B60" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7418,21 +7423,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7446,10 +7451,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540440</v>
+        <v>540396</v>
       </c>
       <c r="R60" t="n">
-        <v>6943388</v>
+        <v>6943402</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7495,12 +7500,12 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>grov gammal brandhögstubbe</t>
+          <t>grov gammal tallåga, upphängd på block</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7522,7 +7527,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119539918</v>
+        <v>119539898</v>
       </c>
       <c r="B61" t="n">
         <v>78171</v>
@@ -7566,10 +7571,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540396</v>
+        <v>540341</v>
       </c>
       <c r="R61" t="n">
-        <v>6943402</v>
+        <v>6943727</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7615,12 +7620,12 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>grov gammal tallåga, upphängd på block</t>
+          <t>gammal tallåga som murknar i ena änden</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7642,10 +7647,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119539898</v>
+        <v>119539903</v>
       </c>
       <c r="B62" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7658,21 +7663,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7686,10 +7691,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540341</v>
+        <v>540360</v>
       </c>
       <c r="R62" t="n">
-        <v>6943727</v>
+        <v>6943524</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7735,12 +7740,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>gammal tallåga som murknar i ena änden</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7762,10 +7762,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119539893</v>
+        <v>119539913</v>
       </c>
       <c r="B63" t="n">
-        <v>90807</v>
+        <v>78263</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7774,30 +7774,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7806,10 +7806,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540290</v>
+        <v>540440</v>
       </c>
       <c r="R63" t="n">
-        <v>6943642</v>
+        <v>6943388</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
+          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
+          <t>grov gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8952,10 +8952,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119539906</v>
+        <v>119539879</v>
       </c>
       <c r="B73" t="n">
-        <v>78171</v>
+        <v>92030</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8968,21 +8968,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8996,10 +8996,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540330</v>
+        <v>540440</v>
       </c>
       <c r="R73" t="n">
-        <v>6943510</v>
+        <v>6943698</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9045,12 +9045,12 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>gammal tallågerest</t>
+          <t>inuti grov, gammal och murken tallåga</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9072,10 +9072,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119539879</v>
+        <v>119539906</v>
       </c>
       <c r="B74" t="n">
-        <v>92030</v>
+        <v>78171</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9088,21 +9088,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540440</v>
+        <v>540330</v>
       </c>
       <c r="R74" t="n">
-        <v>6943698</v>
+        <v>6943510</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>inuti grov, gammal och murken tallåga</t>
+          <t>gammal tallågerest</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9312,10 +9312,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119539905</v>
+        <v>119539886</v>
       </c>
       <c r="B76" t="n">
-        <v>90712</v>
+        <v>79115</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9324,25 +9324,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540322</v>
+        <v>540305</v>
       </c>
       <c r="R76" t="n">
-        <v>6943516</v>
+        <v>6943840</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>50 cm grov gammal tallåga efter fallen bränd torraka, upphängd</t>
+          <t>torr och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9432,10 +9432,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119539886</v>
+        <v>119539905</v>
       </c>
       <c r="B77" t="n">
-        <v>79115</v>
+        <v>90712</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9444,25 +9444,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540305</v>
+        <v>540322</v>
       </c>
       <c r="R77" t="n">
-        <v>6943840</v>
+        <v>6943516</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>torr och hård gammal tallhögstubbe</t>
+          <t>50 cm grov gammal tallåga efter fallen bränd torraka, upphängd</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9552,10 +9552,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119539933</v>
+        <v>119539912</v>
       </c>
       <c r="B78" t="n">
-        <v>91884</v>
+        <v>95455</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9568,21 +9568,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5449</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540460</v>
+        <v>540476</v>
       </c>
       <c r="R78" t="n">
-        <v>6943329</v>
+        <v>6943402</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9645,7 +9645,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
+          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>äldre tallvindfälle</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9667,10 +9672,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119539912</v>
+        <v>119539933</v>
       </c>
       <c r="B79" t="n">
-        <v>95455</v>
+        <v>91884</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9683,21 +9688,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>5449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -9711,10 +9716,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540476</v>
+        <v>540460</v>
       </c>
       <c r="R79" t="n">
-        <v>6943402</v>
+        <v>6943329</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9760,12 +9765,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>äldre tallvindfälle</t>
+          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>

--- a/artfynd/A 13873-2022 artfynd.xlsx
+++ b/artfynd/A 13873-2022 artfynd.xlsx
@@ -3481,7 +3481,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119539937</v>
+        <v>119539892</v>
       </c>
       <c r="B27" t="n">
         <v>78171</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3525,10 +3525,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540485</v>
+        <v>540309</v>
       </c>
       <c r="R27" t="n">
-        <v>6943348</v>
+        <v>6943634</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>bränd rest av gammal tallåga</t>
+          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119539888</v>
+        <v>119539935</v>
       </c>
       <c r="B28" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540375</v>
+        <v>540539</v>
       </c>
       <c r="R28" t="n">
-        <v>6943495</v>
+        <v>6943376</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3694,12 +3694,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>sandfläck med lav</t>
+          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3721,10 +3716,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119539885</v>
+        <v>119539922</v>
       </c>
       <c r="B29" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3737,21 +3732,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3765,10 +3760,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540298</v>
+        <v>540431</v>
       </c>
       <c r="R29" t="n">
-        <v>6943968</v>
+        <v>6943257</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3814,12 +3809,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>sandfläck med lav</t>
+          <t>140-årig tallskog av stavatyp, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3841,10 +3831,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119539917</v>
+        <v>119539885</v>
       </c>
       <c r="B30" t="n">
-        <v>79473</v>
+        <v>91856</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3857,21 +3847,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>388</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3885,10 +3875,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540406</v>
+        <v>540298</v>
       </c>
       <c r="R30" t="n">
-        <v>6943382</v>
+        <v>6943968</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3934,12 +3924,12 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>150-årig asp</t>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3961,10 +3951,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119539878</v>
+        <v>119539893</v>
       </c>
       <c r="B31" t="n">
-        <v>78171</v>
+        <v>90807</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3973,25 +3963,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4005,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540416</v>
+        <v>540290</v>
       </c>
       <c r="R31" t="n">
-        <v>6943681</v>
+        <v>6943642</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4054,12 +4044,12 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>tallågor efter fallna torrakor</t>
+          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4081,10 +4071,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119539889</v>
+        <v>119539905</v>
       </c>
       <c r="B32" t="n">
-        <v>91310</v>
+        <v>90712</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4097,21 +4087,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1958</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4125,10 +4115,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540373</v>
+        <v>540322</v>
       </c>
       <c r="R32" t="n">
-        <v>6943495</v>
+        <v>6943516</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4174,12 +4164,12 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>sandfläck med lav</t>
+          <t>50 cm grov gammal tallåga efter fallen bränd torraka, upphängd</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4201,10 +4191,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119539902</v>
+        <v>119539928</v>
       </c>
       <c r="B33" t="n">
-        <v>91884</v>
+        <v>90488</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4217,21 +4207,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>3242</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4245,10 +4235,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540358</v>
+        <v>540363</v>
       </c>
       <c r="R33" t="n">
-        <v>6943621</v>
+        <v>6943176</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4294,7 +4284,12 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>tallåga av klenare torraka, upphängd mot block</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4316,10 +4311,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119539920</v>
+        <v>119539916</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>90832</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4328,25 +4323,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>72</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Urskogsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neoantrodia primaeva</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4360,10 +4355,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540403</v>
+        <v>540406</v>
       </c>
       <c r="R34" t="n">
-        <v>6943409</v>
+        <v>6943373</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4409,7 +4404,12 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk morän</t>
+          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>gammal bastant tallåga, upphängd på block</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4431,10 +4431,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119539884</v>
+        <v>119539882</v>
       </c>
       <c r="B35" t="n">
-        <v>91832</v>
+        <v>90712</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4443,25 +4443,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>1503</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540340</v>
+        <v>540460</v>
       </c>
       <c r="R35" t="n">
-        <v>6943926</v>
+        <v>6943791</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>sandfläck med lav</t>
+          <t>mycket grov gammal tallåga, upphängd på block</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4551,7 +4551,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119539892</v>
+        <v>119539887</v>
       </c>
       <c r="B36" t="n">
         <v>78171</v>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540309</v>
+        <v>540292</v>
       </c>
       <c r="R36" t="n">
-        <v>6943634</v>
+        <v>6943823</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4644,12 +4644,12 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
+          <t>torr och hård gammal tallåga efter fallen torraka</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4671,10 +4671,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119539900</v>
+        <v>119539931</v>
       </c>
       <c r="B37" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540409</v>
+        <v>540411</v>
       </c>
       <c r="R37" t="n">
-        <v>6943632</v>
+        <v>6943247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4764,12 +4764,12 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>ihålig gammal tallåga</t>
+          <t>gammal fallen torraka</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4791,10 +4791,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119539931</v>
+        <v>119539879</v>
       </c>
       <c r="B38" t="n">
-        <v>79144</v>
+        <v>92030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4807,21 +4807,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540411</v>
+        <v>540440</v>
       </c>
       <c r="R38" t="n">
-        <v>6943247</v>
+        <v>6943698</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4884,12 +4884,12 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>gammal fallen torraka</t>
+          <t>inuti grov, gammal och murken tallåga</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119539883</v>
+        <v>119539901</v>
       </c>
       <c r="B39" t="n">
-        <v>91884</v>
+        <v>79115</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4927,21 +4927,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540356</v>
+        <v>540369</v>
       </c>
       <c r="R39" t="n">
-        <v>6943906</v>
+        <v>6943646</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>sandfläck med lav</t>
+          <t>50 cm grov och hög skorstenshögstubbe med bohål</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119539929</v>
+        <v>119539915</v>
       </c>
       <c r="B40" t="n">
-        <v>91856</v>
+        <v>97907</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5043,25 +5043,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2059</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540360</v>
+        <v>540409</v>
       </c>
       <c r="R40" t="n">
-        <v>6943180</v>
+        <v>6943365</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+          <t>140-årig lövrik tallnaturskog på frisk morän</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119539880</v>
+        <v>119539908</v>
       </c>
       <c r="B41" t="n">
-        <v>78263</v>
+        <v>91856</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5162,34 +5162,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540454</v>
+        <v>540357</v>
       </c>
       <c r="R41" t="n">
-        <v>6943707</v>
+        <v>6943461</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5235,12 +5239,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>brandhögstubbar</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5262,10 +5261,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119539896</v>
+        <v>119539937</v>
       </c>
       <c r="B42" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5278,21 +5277,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5306,10 +5305,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540348</v>
+        <v>540485</v>
       </c>
       <c r="R42" t="n">
-        <v>6943733</v>
+        <v>6943348</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5355,12 +5354,12 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>8 m hög, 50 cm bred skorstenshögstubbe med brandspår</t>
+          <t>bränd rest av gammal tallåga</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5382,10 +5381,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119539925</v>
+        <v>119539886</v>
       </c>
       <c r="B43" t="n">
-        <v>78263</v>
+        <v>79115</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5398,26 +5397,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5426,10 +5425,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540347</v>
+        <v>540305</v>
       </c>
       <c r="R43" t="n">
-        <v>6943300</v>
+        <v>6943840</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5475,12 +5474,12 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>brandhögstubbar</t>
+          <t>torr och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5502,10 +5501,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119539919</v>
+        <v>119539938</v>
       </c>
       <c r="B44" t="n">
-        <v>87406</v>
+        <v>78171</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5518,21 +5517,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4412</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5546,10 +5545,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540405</v>
+        <v>540548</v>
       </c>
       <c r="R44" t="n">
-        <v>6943390</v>
+        <v>6943249</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5595,7 +5594,12 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>gammal ihålig rest av grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5617,10 +5621,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119539935</v>
+        <v>119539917</v>
       </c>
       <c r="B45" t="n">
-        <v>91884</v>
+        <v>79473</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5633,21 +5637,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>388</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5661,10 +5665,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540539</v>
+        <v>540406</v>
       </c>
       <c r="R45" t="n">
-        <v>6943376</v>
+        <v>6943382</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5710,7 +5714,12 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
+          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>150-årig asp</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5732,10 +5741,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119539907</v>
+        <v>119539936</v>
       </c>
       <c r="B46" t="n">
-        <v>89633</v>
+        <v>78171</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5748,21 +5757,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5776,10 +5785,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540357</v>
+        <v>540517</v>
       </c>
       <c r="R46" t="n">
-        <v>6943462</v>
+        <v>6943388</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5825,12 +5834,12 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>gammal murken tallåga</t>
+          <t>grov gammal tallåga, hängande på block</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5852,10 +5861,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119539914</v>
+        <v>119539884</v>
       </c>
       <c r="B47" t="n">
-        <v>79144</v>
+        <v>91832</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5868,21 +5877,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5896,10 +5905,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540410</v>
+        <v>540340</v>
       </c>
       <c r="R47" t="n">
-        <v>6943365</v>
+        <v>6943926</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5945,12 +5954,12 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>grov gammal skorstenshögstubbe</t>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5972,10 +5981,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119539899</v>
+        <v>119539919</v>
       </c>
       <c r="B48" t="n">
-        <v>90807</v>
+        <v>87406</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5984,25 +5993,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>65</v>
+        <v>4412</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6016,10 +6025,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540341</v>
+        <v>540405</v>
       </c>
       <c r="R48" t="n">
-        <v>6943727</v>
+        <v>6943390</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6065,12 +6074,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>gammal tallåga som murknar i ena änden</t>
+          <t>140-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6092,10 +6096,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119539936</v>
+        <v>119539876</v>
       </c>
       <c r="B49" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6108,21 +6112,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6136,10 +6140,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540517</v>
+        <v>540495</v>
       </c>
       <c r="R49" t="n">
-        <v>6943388</v>
+        <v>6943516</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6190,7 +6194,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>grov gammal tallåga, hängande på block</t>
+          <t>sandig fläck</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6332,10 +6336,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119539932</v>
+        <v>119539906</v>
       </c>
       <c r="B51" t="n">
-        <v>80483</v>
+        <v>78171</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6348,21 +6352,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6376,10 +6380,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540431</v>
+        <v>540330</v>
       </c>
       <c r="R51" t="n">
-        <v>6943279</v>
+        <v>6943510</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6425,12 +6429,12 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>gammal torraka med avfallande splint, 30 cm bred</t>
+          <t>gammal tallågerest</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6452,10 +6456,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119539938</v>
+        <v>119539902</v>
       </c>
       <c r="B52" t="n">
-        <v>78171</v>
+        <v>91884</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6468,21 +6472,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6496,10 +6500,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540548</v>
+        <v>540358</v>
       </c>
       <c r="R52" t="n">
-        <v>6943249</v>
+        <v>6943621</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6545,12 +6549,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>gammal ihålig rest av grov gammal tallåga</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6572,10 +6571,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119539901</v>
+        <v>119539934</v>
       </c>
       <c r="B53" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6588,21 +6587,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6616,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540369</v>
+        <v>540502</v>
       </c>
       <c r="R53" t="n">
-        <v>6943646</v>
+        <v>6943408</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6665,12 +6664,12 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>50 cm grov och hög skorstenshögstubbe med bohål</t>
+          <t>grov gammal tallhögstubbe med kolade ytor</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6692,10 +6691,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119539890</v>
+        <v>119539930</v>
       </c>
       <c r="B54" t="n">
-        <v>91834</v>
+        <v>92030</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6708,21 +6707,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6736,10 +6735,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540393</v>
+        <v>540379</v>
       </c>
       <c r="R54" t="n">
-        <v>6943526</v>
+        <v>6943193</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6785,7 +6784,12 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>äldre tallstock</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6807,10 +6811,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119539909</v>
+        <v>119539911</v>
       </c>
       <c r="B55" t="n">
-        <v>78171</v>
+        <v>86410</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6819,25 +6823,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>249228</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6851,10 +6855,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540370</v>
+        <v>540428</v>
       </c>
       <c r="R55" t="n">
-        <v>6943446</v>
+        <v>6943428</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6900,12 +6904,12 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>grov gammal tallågerest</t>
+          <t>barrmatta under grov gran</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6927,10 +6931,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119539895</v>
+        <v>119539904</v>
       </c>
       <c r="B56" t="n">
-        <v>90712</v>
+        <v>92030</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6939,25 +6943,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6971,10 +6975,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540287</v>
+        <v>540327</v>
       </c>
       <c r="R56" t="n">
-        <v>6943686</v>
+        <v>6943521</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7020,12 +7024,12 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>gammal murken rest av tallåga</t>
+          <t>gammal tallågerest med brandspår</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7047,10 +7051,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119539882</v>
+        <v>119539883</v>
       </c>
       <c r="B57" t="n">
-        <v>90712</v>
+        <v>91884</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7059,25 +7063,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1503</v>
+        <v>5449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7091,10 +7095,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540460</v>
+        <v>540356</v>
       </c>
       <c r="R57" t="n">
-        <v>6943791</v>
+        <v>6943906</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7145,7 +7149,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>mycket grov gammal tallåga, upphängd på block</t>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7167,10 +7171,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119539911</v>
+        <v>119539929</v>
       </c>
       <c r="B58" t="n">
-        <v>86410</v>
+        <v>91856</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7179,25 +7183,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>249228</v>
+        <v>2059</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -7211,10 +7215,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540428</v>
+        <v>540360</v>
       </c>
       <c r="R58" t="n">
-        <v>6943428</v>
+        <v>6943180</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7260,12 +7264,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>barrmatta under grov gran</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7287,10 +7286,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119539893</v>
+        <v>119539896</v>
       </c>
       <c r="B59" t="n">
-        <v>90807</v>
+        <v>78263</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7299,30 +7298,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7331,10 +7330,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540290</v>
+        <v>540348</v>
       </c>
       <c r="R59" t="n">
-        <v>6943642</v>
+        <v>6943733</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7380,12 +7379,12 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
+          <t>8 m hög, 50 cm bred skorstenshögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7407,10 +7406,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119539918</v>
+        <v>119539921</v>
       </c>
       <c r="B60" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7423,21 +7422,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7451,10 +7450,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540396</v>
+        <v>540400</v>
       </c>
       <c r="R60" t="n">
-        <v>6943402</v>
+        <v>6943414</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7500,12 +7499,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>grov gammal tallåga, upphängd på block</t>
+          <t>140-årig lövrik tallnaturskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7527,10 +7521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119539898</v>
+        <v>119539914</v>
       </c>
       <c r="B61" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7543,21 +7537,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7571,10 +7565,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540341</v>
+        <v>540410</v>
       </c>
       <c r="R61" t="n">
-        <v>6943727</v>
+        <v>6943365</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7620,12 +7614,12 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>gammal tallåga som murknar i ena änden</t>
+          <t>grov gammal skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7647,10 +7641,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119539903</v>
+        <v>119539912</v>
       </c>
       <c r="B62" t="n">
-        <v>91856</v>
+        <v>95455</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7663,21 +7657,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2059</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7691,10 +7685,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540360</v>
+        <v>540476</v>
       </c>
       <c r="R62" t="n">
-        <v>6943524</v>
+        <v>6943402</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7740,7 +7734,12 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>äldre tallvindfälle</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7762,10 +7761,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119539913</v>
+        <v>119539909</v>
       </c>
       <c r="B63" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7778,21 +7777,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7806,10 +7805,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540440</v>
+        <v>540370</v>
       </c>
       <c r="R63" t="n">
-        <v>6943388</v>
+        <v>6943446</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7855,12 +7854,12 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>grov gammal brandhögstubbe</t>
+          <t>grov gammal tallågerest</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7882,10 +7881,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119539908</v>
+        <v>119539924</v>
       </c>
       <c r="B64" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7898,21 +7897,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7926,10 +7925,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540357</v>
+        <v>540345</v>
       </c>
       <c r="R64" t="n">
-        <v>6943461</v>
+        <v>6943310</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7975,7 +7974,12 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>lumpad grov gammal talltopp</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7997,10 +8001,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119539876</v>
+        <v>119539899</v>
       </c>
       <c r="B65" t="n">
-        <v>91856</v>
+        <v>90807</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8009,25 +8013,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>65</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -8041,10 +8045,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540495</v>
+        <v>540341</v>
       </c>
       <c r="R65" t="n">
-        <v>6943516</v>
+        <v>6943727</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8090,12 +8094,12 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>sandig fläck</t>
+          <t>gammal tallåga som murknar i ena änden</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8117,7 +8121,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119539924</v>
+        <v>119539878</v>
       </c>
       <c r="B66" t="n">
         <v>78171</v>
@@ -8152,7 +8156,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8161,10 +8165,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540345</v>
+        <v>540416</v>
       </c>
       <c r="R66" t="n">
-        <v>6943310</v>
+        <v>6943681</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8210,12 +8214,12 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>lumpad grov gammal talltopp</t>
+          <t>tallågor efter fallna torrakor</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8237,10 +8241,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119539887</v>
+        <v>119539903</v>
       </c>
       <c r="B67" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8253,21 +8257,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -8281,10 +8285,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540292</v>
+        <v>540360</v>
       </c>
       <c r="R67" t="n">
-        <v>6943823</v>
+        <v>6943524</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8330,12 +8334,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>torr och hård gammal tallåga efter fallen torraka</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8357,10 +8356,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119539926</v>
+        <v>119539910</v>
       </c>
       <c r="B68" t="n">
-        <v>91856</v>
+        <v>89253</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8369,25 +8368,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2059</v>
+        <v>1599</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8401,10 +8400,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540346</v>
+        <v>540408</v>
       </c>
       <c r="R68" t="n">
-        <v>6943281</v>
+        <v>6943426</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8445,12 +8444,18 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>lågörtsmark</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8472,10 +8477,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119539904</v>
+        <v>119539894</v>
       </c>
       <c r="B69" t="n">
-        <v>92030</v>
+        <v>90712</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8484,25 +8489,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8516,10 +8521,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540327</v>
+        <v>540290</v>
       </c>
       <c r="R69" t="n">
-        <v>6943521</v>
+        <v>6943659</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8565,12 +8570,12 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>gammal tallågerest med brandspår</t>
+          <t>grov gammal tallåga, upphängd på block</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8712,10 +8717,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119539894</v>
+        <v>119539907</v>
       </c>
       <c r="B71" t="n">
-        <v>90712</v>
+        <v>89633</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8724,25 +8729,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8756,10 +8761,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540290</v>
+        <v>540357</v>
       </c>
       <c r="R71" t="n">
-        <v>6943659</v>
+        <v>6943462</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8805,12 +8810,12 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>grov gammal tallåga, upphängd på block</t>
+          <t>gammal murken tallåga</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8832,10 +8837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119539934</v>
+        <v>119539890</v>
       </c>
       <c r="B72" t="n">
-        <v>78262</v>
+        <v>91834</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8848,21 +8853,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8876,10 +8881,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540502</v>
+        <v>540393</v>
       </c>
       <c r="R72" t="n">
-        <v>6943408</v>
+        <v>6943526</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8926,11 +8931,6 @@
       <c r="AI72" t="inlineStr">
         <is>
           <t>140-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>grov gammal tallhögstubbe med kolade ytor</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8952,10 +8952,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119539879</v>
+        <v>119539925</v>
       </c>
       <c r="B73" t="n">
-        <v>92030</v>
+        <v>78263</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8968,26 +8968,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8996,10 +8996,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540440</v>
+        <v>540347</v>
       </c>
       <c r="R73" t="n">
-        <v>6943698</v>
+        <v>6943300</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9045,12 +9045,12 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>inuti grov, gammal och murken tallåga</t>
+          <t>brandhögstubbar</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9072,10 +9072,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119539906</v>
+        <v>119539888</v>
       </c>
       <c r="B74" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9088,21 +9088,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540330</v>
+        <v>540375</v>
       </c>
       <c r="R74" t="n">
-        <v>6943510</v>
+        <v>6943495</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>gammal tallågerest</t>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9192,10 +9192,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119539928</v>
+        <v>119539895</v>
       </c>
       <c r="B75" t="n">
-        <v>90488</v>
+        <v>90712</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9204,25 +9204,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9236,10 +9236,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540363</v>
+        <v>540287</v>
       </c>
       <c r="R75" t="n">
-        <v>6943176</v>
+        <v>6943686</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9285,12 +9285,12 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>tallåga av klenare torraka, upphängd mot block</t>
+          <t>gammal murken rest av tallåga</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9312,10 +9312,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119539886</v>
+        <v>119539881</v>
       </c>
       <c r="B76" t="n">
-        <v>79115</v>
+        <v>90807</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9324,25 +9324,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540305</v>
+        <v>540423</v>
       </c>
       <c r="R76" t="n">
-        <v>6943840</v>
+        <v>6943766</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>torr och hård gammal tallhögstubbe</t>
+          <t>bränd tallågerest</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9432,10 +9432,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119539905</v>
+        <v>119539900</v>
       </c>
       <c r="B77" t="n">
-        <v>90712</v>
+        <v>78171</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9444,25 +9444,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540322</v>
+        <v>540409</v>
       </c>
       <c r="R77" t="n">
-        <v>6943516</v>
+        <v>6943632</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>50 cm grov gammal tallåga efter fallen bränd torraka, upphängd</t>
+          <t>ihålig gammal tallåga</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9552,10 +9552,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119539912</v>
+        <v>119539913</v>
       </c>
       <c r="B78" t="n">
-        <v>95455</v>
+        <v>78263</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9568,21 +9568,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540476</v>
+        <v>540440</v>
       </c>
       <c r="R78" t="n">
-        <v>6943402</v>
+        <v>6943388</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9645,12 +9645,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
+          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>äldre tallvindfälle</t>
+          <t>grov gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9672,10 +9672,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119539933</v>
+        <v>119539918</v>
       </c>
       <c r="B79" t="n">
-        <v>91884</v>
+        <v>78171</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9688,21 +9688,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540460</v>
+        <v>540396</v>
       </c>
       <c r="R79" t="n">
-        <v>6943329</v>
+        <v>6943402</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9765,7 +9765,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>grov gammal tallåga, upphängd på block</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9787,10 +9792,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119539915</v>
+        <v>119539898</v>
       </c>
       <c r="B80" t="n">
-        <v>97907</v>
+        <v>78171</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9799,25 +9804,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9831,10 +9836,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540409</v>
+        <v>540341</v>
       </c>
       <c r="R80" t="n">
-        <v>6943365</v>
+        <v>6943727</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9880,7 +9885,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk morän</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>gammal tallåga som murknar i ena änden</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9902,10 +9912,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119539916</v>
+        <v>119539920</v>
       </c>
       <c r="B81" t="n">
-        <v>90832</v>
+        <v>97907</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9914,25 +9924,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>72</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Urskogsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neoantrodia primaeva</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9946,10 +9956,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540406</v>
+        <v>540403</v>
       </c>
       <c r="R81" t="n">
-        <v>6943373</v>
+        <v>6943409</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9995,12 +10005,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>gammal bastant tallåga, upphängd på block</t>
+          <t>140-årig lövrik tallnaturskog på frisk morän</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10022,10 +10027,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119539881</v>
+        <v>119539880</v>
       </c>
       <c r="B82" t="n">
-        <v>90807</v>
+        <v>78263</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10034,42 +10039,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540423</v>
+        <v>540454</v>
       </c>
       <c r="R82" t="n">
-        <v>6943766</v>
+        <v>6943707</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10115,12 +10116,12 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>bränd tallågerest</t>
+          <t>brandhögstubbar</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10142,10 +10143,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119539910</v>
+        <v>119539932</v>
       </c>
       <c r="B83" t="n">
-        <v>89253</v>
+        <v>80483</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10154,25 +10155,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1599</v>
+        <v>1049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -10186,10 +10187,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540408</v>
+        <v>540431</v>
       </c>
       <c r="R83" t="n">
-        <v>6943426</v>
+        <v>6943279</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10230,18 +10231,17 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>lågörtsmark</t>
+          <t>gammal torraka med avfallande splint, 30 cm bred</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10263,10 +10263,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119539930</v>
+        <v>119539933</v>
       </c>
       <c r="B84" t="n">
-        <v>92030</v>
+        <v>91884</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10279,21 +10279,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10307,10 +10307,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540379</v>
+        <v>540460</v>
       </c>
       <c r="R84" t="n">
-        <v>6943193</v>
+        <v>6943329</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10356,12 +10356,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>äldre tallstock</t>
+          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10383,10 +10378,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119539921</v>
+        <v>119539926</v>
       </c>
       <c r="B85" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10399,21 +10394,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10427,10 +10422,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540400</v>
+        <v>540346</v>
       </c>
       <c r="R85" t="n">
-        <v>6943414</v>
+        <v>6943281</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10476,7 +10471,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10498,10 +10493,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119539922</v>
+        <v>119539889</v>
       </c>
       <c r="B86" t="n">
-        <v>91884</v>
+        <v>91310</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10510,25 +10505,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>1958</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -10542,10 +10537,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540431</v>
+        <v>540373</v>
       </c>
       <c r="R86" t="n">
-        <v>6943257</v>
+        <v>6943495</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10591,7 +10586,12 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp, på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>

--- a/artfynd/A 13873-2022 artfynd.xlsx
+++ b/artfynd/A 13873-2022 artfynd.xlsx
@@ -5146,10 +5146,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119539908</v>
+        <v>119539937</v>
       </c>
       <c r="B41" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5162,21 +5162,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540357</v>
+        <v>540485</v>
       </c>
       <c r="R41" t="n">
-        <v>6943461</v>
+        <v>6943348</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5239,7 +5239,12 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>bränd rest av gammal tallåga</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5261,10 +5266,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119539937</v>
+        <v>119539908</v>
       </c>
       <c r="B42" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5277,21 +5282,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5305,10 +5310,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540485</v>
+        <v>540357</v>
       </c>
       <c r="R42" t="n">
-        <v>6943348</v>
+        <v>6943461</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5354,12 +5359,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>bränd rest av gammal tallåga</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119539886</v>
+        <v>119539938</v>
       </c>
       <c r="B43" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5397,21 +5397,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540305</v>
+        <v>540548</v>
       </c>
       <c r="R43" t="n">
-        <v>6943840</v>
+        <v>6943249</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>torr och hård gammal tallhögstubbe</t>
+          <t>gammal ihålig rest av grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119539938</v>
+        <v>119539917</v>
       </c>
       <c r="B44" t="n">
-        <v>78171</v>
+        <v>79473</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5517,21 +5517,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>388</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540548</v>
+        <v>540406</v>
       </c>
       <c r="R44" t="n">
-        <v>6943249</v>
+        <v>6943382</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>gammal ihålig rest av grov gammal tallåga</t>
+          <t>150-årig asp</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119539917</v>
+        <v>119539936</v>
       </c>
       <c r="B45" t="n">
-        <v>79473</v>
+        <v>78171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5637,21 +5637,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540406</v>
+        <v>540517</v>
       </c>
       <c r="R45" t="n">
-        <v>6943382</v>
+        <v>6943388</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>150-årig asp</t>
+          <t>grov gammal tallåga, hängande på block</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119539936</v>
+        <v>119539886</v>
       </c>
       <c r="B46" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5757,21 +5757,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540517</v>
+        <v>540305</v>
       </c>
       <c r="R46" t="n">
-        <v>6943388</v>
+        <v>6943840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>grov gammal tallåga, hängande på block</t>
+          <t>torr och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119539884</v>
+        <v>119539876</v>
       </c>
       <c r="B47" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5877,21 +5877,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5905,10 +5905,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540340</v>
+        <v>540495</v>
       </c>
       <c r="R47" t="n">
-        <v>6943926</v>
+        <v>6943516</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>sandfläck med lav</t>
+          <t>sandig fläck</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119539876</v>
+        <v>119539884</v>
       </c>
       <c r="B49" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6112,21 +6112,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540495</v>
+        <v>540340</v>
       </c>
       <c r="R49" t="n">
-        <v>6943516</v>
+        <v>6943926</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>sandig fläck</t>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7286,10 +7286,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119539896</v>
+        <v>119539912</v>
       </c>
       <c r="B59" t="n">
-        <v>78263</v>
+        <v>95455</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540348</v>
+        <v>540476</v>
       </c>
       <c r="R59" t="n">
-        <v>6943733</v>
+        <v>6943402</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>8 m hög, 50 cm bred skorstenshögstubbe med brandspår</t>
+          <t>äldre tallvindfälle</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119539921</v>
+        <v>119539914</v>
       </c>
       <c r="B60" t="n">
-        <v>91834</v>
+        <v>79144</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540400</v>
+        <v>540410</v>
       </c>
       <c r="R60" t="n">
-        <v>6943414</v>
+        <v>6943365</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7499,7 +7499,12 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog</t>
+          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>grov gammal skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7521,10 +7526,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119539914</v>
+        <v>119539896</v>
       </c>
       <c r="B61" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7537,21 +7542,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7565,10 +7570,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540410</v>
+        <v>540348</v>
       </c>
       <c r="R61" t="n">
-        <v>6943365</v>
+        <v>6943733</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7614,12 +7619,12 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>grov gammal skorstenshögstubbe</t>
+          <t>8 m hög, 50 cm bred skorstenshögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7641,10 +7646,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119539912</v>
+        <v>119539921</v>
       </c>
       <c r="B62" t="n">
-        <v>95455</v>
+        <v>91834</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7657,21 +7662,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>4362</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7685,10 +7690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540476</v>
+        <v>540400</v>
       </c>
       <c r="R62" t="n">
-        <v>6943402</v>
+        <v>6943414</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7734,12 +7739,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>äldre tallvindfälle</t>
+          <t>140-årig lövrik tallnaturskog</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8597,10 +8597,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119539891</v>
+        <v>119539890</v>
       </c>
       <c r="B70" t="n">
-        <v>92030</v>
+        <v>91834</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8613,21 +8613,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8641,10 +8641,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540309</v>
+        <v>540393</v>
       </c>
       <c r="R70" t="n">
-        <v>6943634</v>
+        <v>6943526</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8690,12 +8690,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>grov tallåga av fallen torraka, upphängd på block</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8717,10 +8712,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119539907</v>
+        <v>119539891</v>
       </c>
       <c r="B71" t="n">
-        <v>89633</v>
+        <v>92030</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8733,21 +8728,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8761,10 +8756,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540357</v>
+        <v>540309</v>
       </c>
       <c r="R71" t="n">
-        <v>6943462</v>
+        <v>6943634</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8810,12 +8805,12 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>gammal murken tallåga</t>
+          <t>grov tallåga av fallen torraka, upphängd på block</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8837,10 +8832,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119539890</v>
+        <v>119539907</v>
       </c>
       <c r="B72" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8853,21 +8848,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8881,10 +8876,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540393</v>
+        <v>540357</v>
       </c>
       <c r="R72" t="n">
-        <v>6943526</v>
+        <v>6943462</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8930,7 +8925,12 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>gammal murken tallåga</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10263,10 +10263,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119539933</v>
+        <v>119539926</v>
       </c>
       <c r="B84" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10279,21 +10279,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10307,10 +10307,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540460</v>
+        <v>540346</v>
       </c>
       <c r="R84" t="n">
-        <v>6943329</v>
+        <v>6943281</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10378,10 +10378,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119539926</v>
+        <v>119539889</v>
       </c>
       <c r="B85" t="n">
-        <v>91856</v>
+        <v>91310</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10390,25 +10390,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2059</v>
+        <v>1958</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540346</v>
+        <v>540373</v>
       </c>
       <c r="R85" t="n">
-        <v>6943281</v>
+        <v>6943495</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10471,7 +10471,12 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10493,10 +10498,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119539889</v>
+        <v>119539933</v>
       </c>
       <c r="B86" t="n">
-        <v>91310</v>
+        <v>91884</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10505,25 +10510,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1958</v>
+        <v>5449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -10537,10 +10542,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540373</v>
+        <v>540460</v>
       </c>
       <c r="R86" t="n">
-        <v>6943495</v>
+        <v>6943329</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10586,12 +10591,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>sandfläck med lav</t>
+          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>

--- a/artfynd/A 13873-2022 artfynd.xlsx
+++ b/artfynd/A 13873-2022 artfynd.xlsx
@@ -3481,10 +3481,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119539892</v>
+        <v>119539911</v>
       </c>
       <c r="B27" t="n">
-        <v>78171</v>
+        <v>86410</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3493,30 +3493,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>249228</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3525,10 +3525,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540309</v>
+        <v>540428</v>
       </c>
       <c r="R27" t="n">
-        <v>6943634</v>
+        <v>6943428</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
+          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
+          <t>barrmatta under grov gran</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119539935</v>
+        <v>119539885</v>
       </c>
       <c r="B28" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540539</v>
+        <v>540298</v>
       </c>
       <c r="R28" t="n">
-        <v>6943376</v>
+        <v>6943968</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3694,7 +3694,12 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
+          <t>140-årig tallskog på frisk rismark</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3716,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119539922</v>
+        <v>119539925</v>
       </c>
       <c r="B29" t="n">
-        <v>91884</v>
+        <v>78263</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3732,26 +3737,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3760,10 +3765,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540431</v>
+        <v>540347</v>
       </c>
       <c r="R29" t="n">
-        <v>6943257</v>
+        <v>6943300</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3809,7 +3814,12 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp, på blockig torr moränmark</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>brandhögstubbar</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3831,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119539885</v>
+        <v>119539930</v>
       </c>
       <c r="B30" t="n">
-        <v>91856</v>
+        <v>92030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3847,21 +3857,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3875,10 +3885,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540298</v>
+        <v>540379</v>
       </c>
       <c r="R30" t="n">
-        <v>6943968</v>
+        <v>6943193</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3924,12 +3934,12 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>sandfläck med lav</t>
+          <t>äldre tallstock</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3951,10 +3961,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119539893</v>
+        <v>119539876</v>
       </c>
       <c r="B31" t="n">
-        <v>90807</v>
+        <v>91856</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3963,30 +3973,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>65</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3995,10 +4005,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540290</v>
+        <v>540495</v>
       </c>
       <c r="R31" t="n">
-        <v>6943642</v>
+        <v>6943516</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,12 +4054,12 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
+          <t>sandig fläck</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4071,10 +4081,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119539905</v>
+        <v>119539931</v>
       </c>
       <c r="B32" t="n">
-        <v>90712</v>
+        <v>79144</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4083,25 +4093,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4115,10 +4125,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540322</v>
+        <v>540411</v>
       </c>
       <c r="R32" t="n">
-        <v>6943516</v>
+        <v>6943247</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4164,12 +4174,12 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>50 cm grov gammal tallåga efter fallen bränd torraka, upphängd</t>
+          <t>gammal fallen torraka</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4191,10 +4201,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119539928</v>
+        <v>119539924</v>
       </c>
       <c r="B33" t="n">
-        <v>90488</v>
+        <v>78171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4207,21 +4217,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4235,10 +4245,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540363</v>
+        <v>540345</v>
       </c>
       <c r="R33" t="n">
-        <v>6943176</v>
+        <v>6943310</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4289,7 +4299,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>tallåga av klenare torraka, upphängd mot block</t>
+          <t>lumpad grov gammal talltopp</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4311,10 +4321,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119539916</v>
+        <v>119539914</v>
       </c>
       <c r="B34" t="n">
-        <v>90832</v>
+        <v>79144</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4323,25 +4333,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>72</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Urskogsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neoantrodia primaeva</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4355,10 +4365,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540406</v>
+        <v>540410</v>
       </c>
       <c r="R34" t="n">
-        <v>6943373</v>
+        <v>6943365</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4404,12 +4414,12 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
+          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>gammal bastant tallåga, upphängd på block</t>
+          <t>grov gammal skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4431,10 +4441,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119539882</v>
+        <v>119539878</v>
       </c>
       <c r="B35" t="n">
-        <v>90712</v>
+        <v>78171</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4443,30 +4453,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4475,10 +4485,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540460</v>
+        <v>540416</v>
       </c>
       <c r="R35" t="n">
-        <v>6943791</v>
+        <v>6943681</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4524,12 +4534,12 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>mycket grov gammal tallåga, upphängd på block</t>
+          <t>tallågor efter fallna torrakor</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4551,10 +4561,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119539887</v>
+        <v>119539884</v>
       </c>
       <c r="B36" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4567,21 +4577,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4595,10 +4605,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540292</v>
+        <v>540340</v>
       </c>
       <c r="R36" t="n">
-        <v>6943823</v>
+        <v>6943926</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4644,12 +4654,12 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>torr och hård gammal tallåga efter fallen torraka</t>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4671,10 +4681,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119539931</v>
+        <v>119539922</v>
       </c>
       <c r="B37" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4687,21 +4697,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4715,10 +4725,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540411</v>
+        <v>540431</v>
       </c>
       <c r="R37" t="n">
-        <v>6943247</v>
+        <v>6943257</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4764,12 +4774,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>gammal fallen torraka</t>
+          <t>140-årig tallskog av stavatyp, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4791,10 +4796,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119539879</v>
+        <v>119539893</v>
       </c>
       <c r="B38" t="n">
-        <v>92030</v>
+        <v>90807</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4803,30 +4808,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4835,10 +4840,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540440</v>
+        <v>540290</v>
       </c>
       <c r="R38" t="n">
-        <v>6943698</v>
+        <v>6943642</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4884,12 +4889,12 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>inuti grov, gammal och murken tallåga</t>
+          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4911,10 +4916,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119539901</v>
+        <v>119539882</v>
       </c>
       <c r="B39" t="n">
-        <v>79115</v>
+        <v>90712</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4923,25 +4928,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4955,10 +4960,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540369</v>
+        <v>540460</v>
       </c>
       <c r="R39" t="n">
-        <v>6943646</v>
+        <v>6943791</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5004,12 +5009,12 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>50 cm grov och hög skorstenshögstubbe med bohål</t>
+          <t>mycket grov gammal tallåga, upphängd på block</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5031,10 +5036,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119539915</v>
+        <v>119539921</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>91834</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5043,25 +5048,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5075,10 +5080,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540409</v>
+        <v>540400</v>
       </c>
       <c r="R40" t="n">
-        <v>6943365</v>
+        <v>6943414</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5124,7 +5129,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk morän</t>
+          <t>140-årig lövrik tallnaturskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5146,7 +5151,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119539937</v>
+        <v>119539909</v>
       </c>
       <c r="B41" t="n">
         <v>78171</v>
@@ -5190,10 +5195,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540485</v>
+        <v>540370</v>
       </c>
       <c r="R41" t="n">
-        <v>6943348</v>
+        <v>6943446</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5239,12 +5244,12 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>bränd rest av gammal tallåga</t>
+          <t>grov gammal tallågerest</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5266,10 +5271,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119539908</v>
+        <v>119539898</v>
       </c>
       <c r="B42" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5282,21 +5287,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5310,10 +5315,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540357</v>
+        <v>540341</v>
       </c>
       <c r="R42" t="n">
-        <v>6943461</v>
+        <v>6943727</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5359,7 +5364,12 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>gammal tallåga som murknar i ena änden</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5381,7 +5391,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119539938</v>
+        <v>119539877</v>
       </c>
       <c r="B43" t="n">
         <v>78171</v>
@@ -5425,10 +5435,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540548</v>
+        <v>540487</v>
       </c>
       <c r="R43" t="n">
-        <v>6943249</v>
+        <v>6943562</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5479,7 +5489,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>gammal ihålig rest av grov gammal tallåga</t>
+          <t>gammal grov tallåga</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5501,10 +5511,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119539917</v>
+        <v>119539932</v>
       </c>
       <c r="B44" t="n">
-        <v>79473</v>
+        <v>80483</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5517,21 +5527,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>388</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5545,10 +5555,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540406</v>
+        <v>540431</v>
       </c>
       <c r="R44" t="n">
-        <v>6943382</v>
+        <v>6943279</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5594,12 +5604,12 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>150-årig asp</t>
+          <t>gammal torraka med avfallande splint, 30 cm bred</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5621,10 +5631,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119539936</v>
+        <v>119539908</v>
       </c>
       <c r="B45" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5637,21 +5647,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5665,10 +5675,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540517</v>
+        <v>540357</v>
       </c>
       <c r="R45" t="n">
-        <v>6943388</v>
+        <v>6943461</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5714,12 +5724,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>grov gammal tallåga, hängande på block</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5741,10 +5746,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119539886</v>
+        <v>119539880</v>
       </c>
       <c r="B46" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5757,38 +5762,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540305</v>
+        <v>540454</v>
       </c>
       <c r="R46" t="n">
-        <v>6943840</v>
+        <v>6943707</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5834,12 +5835,12 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>torr och hård gammal tallhögstubbe</t>
+          <t>brandhögstubbar</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5861,10 +5862,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119539876</v>
+        <v>119539936</v>
       </c>
       <c r="B47" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5877,21 +5878,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5905,10 +5906,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540495</v>
+        <v>540517</v>
       </c>
       <c r="R47" t="n">
-        <v>6943516</v>
+        <v>6943388</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5959,7 +5960,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>sandig fläck</t>
+          <t>grov gammal tallåga, hängande på block</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5981,10 +5982,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119539919</v>
+        <v>119539938</v>
       </c>
       <c r="B48" t="n">
-        <v>87406</v>
+        <v>78171</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5997,21 +5998,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4412</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6025,10 +6026,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540405</v>
+        <v>540548</v>
       </c>
       <c r="R48" t="n">
-        <v>6943390</v>
+        <v>6943249</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6074,7 +6075,12 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>gammal ihålig rest av grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6096,10 +6102,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119539884</v>
+        <v>119539917</v>
       </c>
       <c r="B49" t="n">
-        <v>91832</v>
+        <v>79473</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6112,21 +6118,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>388</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6140,10 +6146,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540340</v>
+        <v>540406</v>
       </c>
       <c r="R49" t="n">
-        <v>6943926</v>
+        <v>6943382</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6189,12 +6195,12 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>sandfläck med lav</t>
+          <t>150-årig asp</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6216,7 +6222,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119539877</v>
+        <v>119539937</v>
       </c>
       <c r="B50" t="n">
         <v>78171</v>
@@ -6260,10 +6266,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540487</v>
+        <v>540485</v>
       </c>
       <c r="R50" t="n">
-        <v>6943562</v>
+        <v>6943348</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6314,7 +6320,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>gammal grov tallåga</t>
+          <t>bränd rest av gammal tallåga</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6336,10 +6342,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119539906</v>
+        <v>119539935</v>
       </c>
       <c r="B51" t="n">
-        <v>78171</v>
+        <v>91884</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6352,21 +6358,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6380,10 +6386,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540330</v>
+        <v>540539</v>
       </c>
       <c r="R51" t="n">
-        <v>6943510</v>
+        <v>6943376</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6429,12 +6435,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>gammal tallågerest</t>
+          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6456,10 +6457,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119539902</v>
+        <v>119539896</v>
       </c>
       <c r="B52" t="n">
-        <v>91884</v>
+        <v>78263</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6472,21 +6473,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6500,10 +6501,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540358</v>
+        <v>540348</v>
       </c>
       <c r="R52" t="n">
-        <v>6943621</v>
+        <v>6943733</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6549,7 +6550,12 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>8 m hög, 50 cm bred skorstenshögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6571,10 +6577,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119539934</v>
+        <v>119539889</v>
       </c>
       <c r="B53" t="n">
-        <v>78262</v>
+        <v>91310</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6583,25 +6589,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>1958</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6615,10 +6621,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540502</v>
+        <v>540373</v>
       </c>
       <c r="R53" t="n">
-        <v>6943408</v>
+        <v>6943495</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6669,7 +6675,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>grov gammal tallhögstubbe med kolade ytor</t>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6691,10 +6697,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119539930</v>
+        <v>119539928</v>
       </c>
       <c r="B54" t="n">
-        <v>92030</v>
+        <v>90488</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6707,21 +6713,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6735,10 +6741,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540379</v>
+        <v>540363</v>
       </c>
       <c r="R54" t="n">
-        <v>6943193</v>
+        <v>6943176</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6789,7 +6795,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>äldre tallstock</t>
+          <t>tallåga av klenare torraka, upphängd mot block</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6811,10 +6817,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119539911</v>
+        <v>119539891</v>
       </c>
       <c r="B55" t="n">
-        <v>86410</v>
+        <v>92030</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6823,25 +6829,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>249228</v>
+        <v>2079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6855,10 +6861,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540428</v>
+        <v>540309</v>
       </c>
       <c r="R55" t="n">
-        <v>6943428</v>
+        <v>6943634</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6904,12 +6910,12 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>barrmatta under grov gran</t>
+          <t>grov tallåga av fallen torraka, upphängd på block</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6931,10 +6937,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119539904</v>
+        <v>119539890</v>
       </c>
       <c r="B56" t="n">
-        <v>92030</v>
+        <v>91834</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6947,21 +6953,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6975,10 +6981,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540327</v>
+        <v>540393</v>
       </c>
       <c r="R56" t="n">
-        <v>6943521</v>
+        <v>6943526</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7024,12 +7030,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>gammal tallågerest med brandspår</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7051,10 +7052,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119539883</v>
+        <v>119539910</v>
       </c>
       <c r="B57" t="n">
-        <v>91884</v>
+        <v>89253</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7063,25 +7064,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>1599</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7095,10 +7096,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540356</v>
+        <v>540408</v>
       </c>
       <c r="R57" t="n">
-        <v>6943906</v>
+        <v>6943426</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7139,17 +7140,18 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>sandfläck med lav</t>
+          <t>lågörtsmark</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7171,7 +7173,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119539929</v>
+        <v>119539926</v>
       </c>
       <c r="B58" t="n">
         <v>91856</v>
@@ -7215,10 +7217,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540360</v>
+        <v>540346</v>
       </c>
       <c r="R58" t="n">
-        <v>6943180</v>
+        <v>6943281</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7286,10 +7288,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119539912</v>
+        <v>119539886</v>
       </c>
       <c r="B59" t="n">
-        <v>95455</v>
+        <v>79115</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7302,21 +7304,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -7330,10 +7332,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540476</v>
+        <v>540305</v>
       </c>
       <c r="R59" t="n">
-        <v>6943402</v>
+        <v>6943840</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7379,12 +7381,12 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>äldre tallvindfälle</t>
+          <t>torr och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7406,10 +7408,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119539914</v>
+        <v>119539881</v>
       </c>
       <c r="B60" t="n">
-        <v>79144</v>
+        <v>90807</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7418,25 +7420,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7450,10 +7452,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540410</v>
+        <v>540423</v>
       </c>
       <c r="R60" t="n">
-        <v>6943365</v>
+        <v>6943766</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7499,12 +7501,12 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>grov gammal skorstenshögstubbe</t>
+          <t>bränd tallågerest</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7526,10 +7528,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119539896</v>
+        <v>119539912</v>
       </c>
       <c r="B61" t="n">
-        <v>78263</v>
+        <v>95455</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7542,21 +7544,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7570,10 +7572,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540348</v>
+        <v>540476</v>
       </c>
       <c r="R61" t="n">
-        <v>6943733</v>
+        <v>6943402</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7619,12 +7621,12 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>8 m hög, 50 cm bred skorstenshögstubbe med brandspår</t>
+          <t>äldre tallvindfälle</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7646,10 +7648,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119539921</v>
+        <v>119539915</v>
       </c>
       <c r="B62" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7658,25 +7660,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7690,10 +7692,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540400</v>
+        <v>540409</v>
       </c>
       <c r="R62" t="n">
-        <v>6943414</v>
+        <v>6943365</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7739,7 +7741,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog</t>
+          <t>140-årig lövrik tallnaturskog på frisk morän</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7761,10 +7763,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119539909</v>
+        <v>119539901</v>
       </c>
       <c r="B63" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7777,21 +7779,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7805,10 +7807,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540370</v>
+        <v>540369</v>
       </c>
       <c r="R63" t="n">
-        <v>6943446</v>
+        <v>6943646</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7854,12 +7856,12 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>grov gammal tallågerest</t>
+          <t>50 cm grov och hög skorstenshögstubbe med bohål</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7881,7 +7883,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119539924</v>
+        <v>119539892</v>
       </c>
       <c r="B64" t="n">
         <v>78171</v>
@@ -7916,7 +7918,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7925,10 +7927,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540345</v>
+        <v>540309</v>
       </c>
       <c r="R64" t="n">
-        <v>6943310</v>
+        <v>6943634</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7974,12 +7976,12 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>lumpad grov gammal talltopp</t>
+          <t>gamla grövre tallågor av fallna torrakor, upphängda på block</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8001,10 +8003,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119539899</v>
+        <v>119539907</v>
       </c>
       <c r="B65" t="n">
-        <v>90807</v>
+        <v>89633</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8013,25 +8015,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -8045,10 +8047,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540341</v>
+        <v>540357</v>
       </c>
       <c r="R65" t="n">
-        <v>6943727</v>
+        <v>6943462</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8094,12 +8096,12 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>gammal tallåga som murknar i ena änden</t>
+          <t>gammal murken tallåga</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8121,10 +8123,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119539878</v>
+        <v>119539899</v>
       </c>
       <c r="B66" t="n">
-        <v>78171</v>
+        <v>90807</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8133,30 +8135,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8165,10 +8167,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540416</v>
+        <v>540341</v>
       </c>
       <c r="R66" t="n">
-        <v>6943681</v>
+        <v>6943727</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8214,12 +8216,12 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>tallågor efter fallna torrakor</t>
+          <t>gammal tallåga som murknar i ena änden</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8241,10 +8243,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119539903</v>
+        <v>119539934</v>
       </c>
       <c r="B67" t="n">
-        <v>91856</v>
+        <v>78262</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8257,21 +8259,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -8285,10 +8287,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540360</v>
+        <v>540502</v>
       </c>
       <c r="R67" t="n">
-        <v>6943524</v>
+        <v>6943408</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8334,7 +8336,12 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>grov gammal tallhögstubbe med kolade ytor</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8356,10 +8363,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119539910</v>
+        <v>119539894</v>
       </c>
       <c r="B68" t="n">
-        <v>89253</v>
+        <v>90712</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8372,21 +8379,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1599</v>
+        <v>1503</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8400,10 +8407,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540408</v>
+        <v>540290</v>
       </c>
       <c r="R68" t="n">
-        <v>6943426</v>
+        <v>6943659</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8444,18 +8451,17 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>150-årig lövrik tallnaturskog på frisk, blockig morän i terrängsvacka</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>lågörtsmark</t>
+          <t>grov gammal tallåga, upphängd på block</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8477,10 +8483,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119539894</v>
+        <v>119539883</v>
       </c>
       <c r="B69" t="n">
-        <v>90712</v>
+        <v>91884</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8489,25 +8495,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1503</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8521,10 +8527,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540290</v>
+        <v>540356</v>
       </c>
       <c r="R69" t="n">
-        <v>6943659</v>
+        <v>6943906</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8570,12 +8576,12 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>grov gammal tallåga, upphängd på block</t>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8597,10 +8603,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119539890</v>
+        <v>119539920</v>
       </c>
       <c r="B70" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8609,25 +8615,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8641,10 +8647,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540393</v>
+        <v>540403</v>
       </c>
       <c r="R70" t="n">
-        <v>6943526</v>
+        <v>6943409</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8690,7 +8696,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig lövrik tallnaturskog på frisk morän</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8712,10 +8718,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119539891</v>
+        <v>119539916</v>
       </c>
       <c r="B71" t="n">
-        <v>92030</v>
+        <v>90832</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8724,25 +8730,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>72</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Urskogsticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Neoantrodia primaeva</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8756,10 +8762,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540309</v>
+        <v>540406</v>
       </c>
       <c r="R71" t="n">
-        <v>6943634</v>
+        <v>6943373</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8805,12 +8811,12 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall på blockig morän</t>
+          <t>150-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>grov tallåga av fallen torraka, upphängd på block</t>
+          <t>gammal bastant tallåga, upphängd på block</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8832,10 +8838,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119539907</v>
+        <v>119539902</v>
       </c>
       <c r="B72" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8848,21 +8854,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8876,10 +8882,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540357</v>
+        <v>540358</v>
       </c>
       <c r="R72" t="n">
-        <v>6943462</v>
+        <v>6943621</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8925,12 +8931,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>gammal murken tallåga</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8952,10 +8953,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119539925</v>
+        <v>119539904</v>
       </c>
       <c r="B73" t="n">
-        <v>78263</v>
+        <v>92030</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8968,26 +8969,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8996,10 +8997,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540347</v>
+        <v>540327</v>
       </c>
       <c r="R73" t="n">
-        <v>6943300</v>
+        <v>6943521</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9045,12 +9046,12 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>brandhögstubbar</t>
+          <t>gammal tallågerest med brandspår</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9072,10 +9073,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119539888</v>
+        <v>119539879</v>
       </c>
       <c r="B74" t="n">
-        <v>91856</v>
+        <v>92030</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9088,21 +9089,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2059</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9116,10 +9117,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540375</v>
+        <v>540440</v>
       </c>
       <c r="R74" t="n">
-        <v>6943495</v>
+        <v>6943698</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9165,12 +9166,12 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig tallskog på frisk rismark</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>sandfläck med lav</t>
+          <t>inuti grov, gammal och murken tallåga</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9192,10 +9193,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119539895</v>
+        <v>119539903</v>
       </c>
       <c r="B75" t="n">
-        <v>90712</v>
+        <v>91856</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9204,25 +9205,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1503</v>
+        <v>2059</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9236,10 +9237,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540287</v>
+        <v>540360</v>
       </c>
       <c r="R75" t="n">
-        <v>6943686</v>
+        <v>6943524</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9285,12 +9286,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>gammal murken rest av tallåga</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9312,10 +9308,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119539881</v>
+        <v>119539887</v>
       </c>
       <c r="B76" t="n">
-        <v>90807</v>
+        <v>78171</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9324,25 +9320,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9356,10 +9352,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540423</v>
+        <v>540292</v>
       </c>
       <c r="R76" t="n">
-        <v>6943766</v>
+        <v>6943823</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9410,7 +9406,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>bränd tallågerest</t>
+          <t>torr och hård gammal tallåga efter fallen torraka</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9432,7 +9428,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119539900</v>
+        <v>119539906</v>
       </c>
       <c r="B77" t="n">
         <v>78171</v>
@@ -9476,10 +9472,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540409</v>
+        <v>540330</v>
       </c>
       <c r="R77" t="n">
-        <v>6943632</v>
+        <v>6943510</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9525,12 +9521,12 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>ihålig gammal tallåga</t>
+          <t>gammal tallågerest</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9552,10 +9548,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119539913</v>
+        <v>119539888</v>
       </c>
       <c r="B78" t="n">
-        <v>78263</v>
+        <v>91856</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9568,21 +9564,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9596,10 +9592,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540440</v>
+        <v>540375</v>
       </c>
       <c r="R78" t="n">
-        <v>6943388</v>
+        <v>6943495</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9645,12 +9641,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
+          <t>140-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>grov gammal brandhögstubbe</t>
+          <t>sandfläck med lav</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9672,10 +9668,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119539918</v>
+        <v>119539913</v>
       </c>
       <c r="B79" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9688,21 +9684,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -9716,10 +9712,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540396</v>
+        <v>540440</v>
       </c>
       <c r="R79" t="n">
-        <v>6943402</v>
+        <v>6943388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9765,12 +9761,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>150-årig tallskog på blockig torr moränmark</t>
+          <t>140-årig lövrik tallnaturskog på frisk, blockig morän</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>grov gammal tallåga, upphängd på block</t>
+          <t>grov gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9792,7 +9788,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119539898</v>
+        <v>119539900</v>
       </c>
       <c r="B80" t="n">
         <v>78171</v>
@@ -9836,10 +9832,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540341</v>
+        <v>540409</v>
       </c>
       <c r="R80" t="n">
-        <v>6943727</v>
+        <v>6943632</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9885,12 +9881,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
+          <t>140-årig tallskog av stavatyp på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>gammal tallåga som murknar i ena änden</t>
+          <t>ihålig gammal tallåga</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9912,10 +9908,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119539920</v>
+        <v>119539918</v>
       </c>
       <c r="B81" t="n">
-        <v>97907</v>
+        <v>78171</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9924,25 +9920,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9956,10 +9952,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540403</v>
+        <v>540396</v>
       </c>
       <c r="R81" t="n">
-        <v>6943409</v>
+        <v>6943402</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10005,7 +10001,12 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>140-årig lövrik tallnaturskog på frisk morän</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>grov gammal tallåga, upphängd på block</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10027,10 +10028,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119539880</v>
+        <v>119539905</v>
       </c>
       <c r="B82" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10039,38 +10040,42 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540454</v>
+        <v>540322</v>
       </c>
       <c r="R82" t="n">
-        <v>6943707</v>
+        <v>6943516</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10116,12 +10121,12 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>140-årig tallskog på frisk rismark</t>
+          <t>150-årig tallskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>brandhögstubbar</t>
+          <t>50 cm grov gammal tallåga efter fallen bränd torraka, upphängd</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10143,10 +10148,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119539932</v>
+        <v>119539895</v>
       </c>
       <c r="B83" t="n">
-        <v>80483</v>
+        <v>90712</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10155,25 +10160,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -10187,10 +10192,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540431</v>
+        <v>540287</v>
       </c>
       <c r="R83" t="n">
-        <v>6943279</v>
+        <v>6943686</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10236,12 +10241,12 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
+          <t>150-årig tallnaturskog med inslag av björk och gammal tall i blockig moränsvacka</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>gammal torraka med avfallande splint, 30 cm bred</t>
+          <t>gammal murken rest av tallåga</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10263,10 +10268,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119539926</v>
+        <v>119539919</v>
       </c>
       <c r="B84" t="n">
-        <v>91856</v>
+        <v>87406</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10279,21 +10284,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2059</v>
+        <v>4412</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10307,10 +10312,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540346</v>
+        <v>540405</v>
       </c>
       <c r="R84" t="n">
-        <v>6943281</v>
+        <v>6943390</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10356,7 +10361,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
+          <t>140-årig lövrik tallnaturskog på frisk morän i terrängsvacka</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10378,10 +10383,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119539889</v>
+        <v>119539933</v>
       </c>
       <c r="B85" t="n">
-        <v>91310</v>
+        <v>91884</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10390,25 +10395,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1958</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10422,10 +10427,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540373</v>
+        <v>540460</v>
       </c>
       <c r="R85" t="n">
-        <v>6943495</v>
+        <v>6943329</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10471,12 +10476,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>sandfläck med lav</t>
+          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10498,10 +10498,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119539933</v>
+        <v>119539929</v>
       </c>
       <c r="B86" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10514,21 +10514,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540460</v>
+        <v>540360</v>
       </c>
       <c r="R86" t="n">
-        <v>6943329</v>
+        <v>6943180</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig torr moränmark med sandfläckar</t>
+          <t>140-årig tallskog med gott om gammal björk, på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
